--- a/pages/shp/uploads/BC 2.7 22-05-2026 - 24-05-2026.xlsx
+++ b/pages/shp/uploads/BC 2.7 22-05-2026 - 24-05-2026.xlsx
@@ -1,34 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EXIM\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9670D9B4-EEA5-4B65-823B-46848BC81E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="HEADER" r:id="rId3" sheetId="1"/>
-    <sheet name="ENTITAS" r:id="rId4" sheetId="2"/>
-    <sheet name="DOKUMEN" r:id="rId5" sheetId="3"/>
-    <sheet name="PENGANGKUT" r:id="rId6" sheetId="4"/>
-    <sheet name="KEMASAN" r:id="rId7" sheetId="5"/>
-    <sheet name="KONTAINER" r:id="rId8" sheetId="6"/>
-    <sheet name="KOMPONENBIAYA" r:id="rId9" sheetId="7"/>
-    <sheet name="BARANG" r:id="rId10" sheetId="8"/>
-    <sheet name="BARANGTARIF" r:id="rId11" sheetId="9"/>
-    <sheet name="BARANGDOKUMEN" r:id="rId12" sheetId="10"/>
-    <sheet name="BARANGENTITAS" r:id="rId13" sheetId="11"/>
-    <sheet name="BARANGSPEKKHUSUS" r:id="rId14" sheetId="12"/>
-    <sheet name="BARANGVD" r:id="rId15" sheetId="13"/>
-    <sheet name="BAHANBAKU" r:id="rId16" sheetId="14"/>
-    <sheet name="BAHANBAKUTARIF" r:id="rId17" sheetId="15"/>
-    <sheet name="BAHANBAKUDOKUMEN" r:id="rId18" sheetId="16"/>
-    <sheet name="PUNGUTAN" r:id="rId19" sheetId="17"/>
-    <sheet name="JAMINAN" r:id="rId20" sheetId="18"/>
-    <sheet name="BANKDEVISA" r:id="rId21" sheetId="19"/>
-    <sheet name="VERSI" r:id="rId22" sheetId="20"/>
-    <sheet name="RESPON" r:id="rId23" sheetId="21"/>
+    <sheet name="HEADER" sheetId="1" r:id="rId1"/>
+    <sheet name="ENTITAS" sheetId="2" r:id="rId2"/>
+    <sheet name="DOKUMEN" sheetId="3" r:id="rId3"/>
+    <sheet name="PENGANGKUT" sheetId="4" r:id="rId4"/>
+    <sheet name="KEMASAN" sheetId="5" r:id="rId5"/>
+    <sheet name="KONTAINER" sheetId="6" r:id="rId6"/>
+    <sheet name="KOMPONENBIAYA" sheetId="7" r:id="rId7"/>
+    <sheet name="BARANG" sheetId="8" r:id="rId8"/>
+    <sheet name="BARANGTARIF" sheetId="9" r:id="rId9"/>
+    <sheet name="BARANGDOKUMEN" sheetId="10" r:id="rId10"/>
+    <sheet name="BARANGENTITAS" sheetId="11" r:id="rId11"/>
+    <sheet name="BARANGSPEKKHUSUS" sheetId="12" r:id="rId12"/>
+    <sheet name="BARANGVD" sheetId="13" r:id="rId13"/>
+    <sheet name="BAHANBAKU" sheetId="14" r:id="rId14"/>
+    <sheet name="BAHANBAKUTARIF" sheetId="15" r:id="rId15"/>
+    <sheet name="BAHANBAKUDOKUMEN" sheetId="16" r:id="rId16"/>
+    <sheet name="PUNGUTAN" sheetId="17" r:id="rId17"/>
+    <sheet name="JAMINAN" sheetId="18" r:id="rId18"/>
+    <sheet name="BANKDEVISA" sheetId="19" r:id="rId19"/>
+    <sheet name="VERSI" sheetId="20" r:id="rId20"/>
+    <sheet name="RESPON" sheetId="21" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1352,19 +1373,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd-MM-yyyy HH:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.00"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.00"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -1391,123 +1412,418 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:DC7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="78" max="78" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="79" max="79" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="83" max="83" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="84" max="84" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="85" max="85" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="86" max="86" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="87" max="87" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="88" max="88" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="89" max="89" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="90" max="90" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="91" max="91" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="92" max="92" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="93" max="93" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="94" max="94" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="95" max="95" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="96" max="96" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="97" max="97" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="98" max="98" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="99" max="99" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="100" max="100" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="101" max="101" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="102" max="102" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="103" max="103" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="104" max="104" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="105" max="105" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="106" max="106" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="107" max="107" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="61" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="92" max="93" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="106" max="107" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:107" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1830,7 +2146,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -1852,53 +2168,53 @@
       <c r="O2" t="s">
         <v>108</v>
       </c>
-      <c r="BK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>4.38783790076E8</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>4.38783790076E8</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB2" t="n">
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>0</v>
+      </c>
+      <c r="BQ2">
+        <v>0</v>
+      </c>
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>438783790.07599998</v>
+      </c>
+      <c r="BW2">
+        <v>1</v>
+      </c>
+      <c r="BY2">
+        <v>438783790.07599998</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2">
         <v>2840.65</v>
       </c>
-      <c r="CC2" t="n">
+      <c r="CC2">
         <v>2840.65</v>
       </c>
-      <c r="CD2" t="n">
-        <v>0.0</v>
+      <c r="CD2">
+        <v>0</v>
       </c>
       <c r="CE2" t="s">
         <v>110</v>
@@ -1921,17 +2237,17 @@
       <c r="CQ2" t="s">
         <v>111</v>
       </c>
-      <c r="CT2" t="n">
-        <v>4.826621691E7</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="CT2">
+        <v>48266216.909999996</v>
+      </c>
+      <c r="CU2">
+        <v>0</v>
+      </c>
+      <c r="CV2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -1953,53 +2269,53 @@
       <c r="O3" t="s">
         <v>108</v>
       </c>
-      <c r="BK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU3" t="n">
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
         <v>3260.43</v>
       </c>
-      <c r="BV3" t="n">
-        <v>5.697601425E7</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>5.697601425E7</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>294.66</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>272.79</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>0.0</v>
+      <c r="BV3">
+        <v>56976014.25</v>
+      </c>
+      <c r="BW3">
+        <v>17475</v>
+      </c>
+      <c r="BY3">
+        <v>56976014.25</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3">
+        <v>294.66000000000003</v>
+      </c>
+      <c r="CC3">
+        <v>272.79000000000002</v>
+      </c>
+      <c r="CD3">
+        <v>0</v>
       </c>
       <c r="CE3" t="s">
         <v>110</v>
@@ -2022,17 +2338,17 @@
       <c r="CQ3" t="s">
         <v>111</v>
       </c>
-      <c r="CT3" t="n">
-        <v>6267361.57</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="CT3">
+        <v>6267361.5700000003</v>
+      </c>
+      <c r="CU3">
+        <v>0</v>
+      </c>
+      <c r="CV3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>120</v>
       </c>
@@ -2054,53 +2370,53 @@
       <c r="O4" t="s">
         <v>108</v>
       </c>
-      <c r="BK4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>4434395.48</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>4434395.48</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB4" t="n">
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>4434395.4800000004</v>
+      </c>
+      <c r="BW4">
+        <v>1</v>
+      </c>
+      <c r="BY4">
+        <v>4434395.4800000004</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4">
         <v>21.1</v>
       </c>
-      <c r="CC4" t="n">
+      <c r="CC4">
         <v>21.1</v>
       </c>
-      <c r="CD4" t="n">
-        <v>0.0</v>
+      <c r="CD4">
+        <v>0</v>
       </c>
       <c r="CE4" t="s">
         <v>110</v>
@@ -2123,17 +2439,17 @@
       <c r="CQ4" t="s">
         <v>111</v>
       </c>
-      <c r="CT4" t="n">
+      <c r="CT4">
         <v>487783.5</v>
       </c>
-      <c r="CU4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="CU4">
+        <v>0</v>
+      </c>
+      <c r="CV4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>122</v>
       </c>
@@ -2155,53 +2471,53 @@
       <c r="O5" t="s">
         <v>108</v>
       </c>
-      <c r="BK5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>2940.0</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>5.13765E7</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>5.13765E7</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>1083.4</v>
-      </c>
-      <c r="CC5" t="n">
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>2940</v>
+      </c>
+      <c r="BV5">
+        <v>51376500</v>
+      </c>
+      <c r="BW5">
+        <v>17475</v>
+      </c>
+      <c r="BY5">
+        <v>51376500</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5">
+        <v>1083.4000000000001</v>
+      </c>
+      <c r="CC5">
         <v>959.43</v>
       </c>
-      <c r="CD5" t="n">
-        <v>0.0</v>
+      <c r="CD5">
+        <v>0</v>
       </c>
       <c r="CE5" t="s">
         <v>110</v>
@@ -2224,17 +2540,17 @@
       <c r="CQ5" t="s">
         <v>111</v>
       </c>
-      <c r="CT5" t="n">
-        <v>5651415.0</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="CT5">
+        <v>5651415</v>
+      </c>
+      <c r="CU5">
+        <v>0</v>
+      </c>
+      <c r="CV5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -2256,53 +2572,53 @@
       <c r="O6" t="s">
         <v>108</v>
       </c>
-      <c r="BK6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU6" t="n">
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
         <v>14730.1</v>
       </c>
-      <c r="BV6" t="n">
-        <v>2.574084975E8</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>2.574084975E8</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB6" t="n">
+      <c r="BV6">
+        <v>257408497.5</v>
+      </c>
+      <c r="BW6">
+        <v>17475</v>
+      </c>
+      <c r="BY6">
+        <v>257408497.5</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6">
         <v>5535.85</v>
       </c>
-      <c r="CC6" t="n">
-        <v>4925.31</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>0.0</v>
+      <c r="CC6">
+        <v>4925.3100000000004</v>
+      </c>
+      <c r="CD6">
+        <v>0</v>
       </c>
       <c r="CE6" t="s">
         <v>110</v>
@@ -2325,17 +2641,17 @@
       <c r="CQ6" t="s">
         <v>111</v>
       </c>
-      <c r="CT6" t="n">
-        <v>2.831493473E7</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="CT6">
+        <v>28314934.73</v>
+      </c>
+      <c r="CU6">
+        <v>0</v>
+      </c>
+      <c r="CV6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>126</v>
       </c>
@@ -2357,53 +2673,53 @@
       <c r="O7" t="s">
         <v>108</v>
       </c>
-      <c r="BK7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU7" t="n">
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
         <v>38418.42</v>
       </c>
-      <c r="BV7" t="n">
-        <v>6.713618895E8</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>6.713618895E8</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>4356.35</v>
-      </c>
-      <c r="CC7" t="n">
+      <c r="BV7">
+        <v>671361889.5</v>
+      </c>
+      <c r="BW7">
+        <v>17475</v>
+      </c>
+      <c r="BY7">
+        <v>671361889.5</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7">
+        <v>4356.3500000000004</v>
+      </c>
+      <c r="CC7">
         <v>3815.25</v>
       </c>
-      <c r="CD7" t="n">
-        <v>0.0</v>
+      <c r="CD7">
+        <v>0</v>
       </c>
       <c r="CE7" t="s">
         <v>110</v>
@@ -2426,41 +2742,37 @@
       <c r="CQ7" t="s">
         <v>111</v>
       </c>
-      <c r="CT7" t="n">
-        <v>7.384980785E7</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>11.0</v>
+      <c r="CT7">
+        <v>73849807.849999994</v>
+      </c>
+      <c r="CU7">
+        <v>0</v>
+      </c>
+      <c r="CV7">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2475,29 +2787,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2509,28 +2817,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2545,32 +2849,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2594,59 +2894,54 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:AO29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="71.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="71.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2771,14 +3066,14 @@
         <v>294</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
@@ -2808,7 +3103,7 @@
       <c r="L2" t="s">
         <v>300</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>114.05</v>
       </c>
       <c r="P2" t="s">
@@ -2826,42 +3121,42 @@
       <c r="T2" t="s">
         <v>349</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2">
         <v>2</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2">
         <v>473.36</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.324468238E7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>13244682.380000001</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
@@ -2891,7 +3186,7 @@
       <c r="L3" t="s">
         <v>300</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>1208.58</v>
       </c>
       <c r="P3" t="s">
@@ -2909,42 +3204,42 @@
       <c r="T3" t="s">
         <v>349</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3">
         <v>3</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3">
         <v>3304.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.902676921E8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>190267692.09999999</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
@@ -2974,7 +3269,7 @@
       <c r="L4" t="s">
         <v>300</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>1428.15</v>
       </c>
       <c r="P4" t="s">
@@ -2992,42 +3287,42 @@
       <c r="T4" t="s">
         <v>349</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4">
         <v>3</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4">
         <v>3304.5</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.24834768466E8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>224834768.46599999</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>104</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
@@ -3057,7 +3352,7 @@
       <c r="L5" t="s">
         <v>300</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>89.87</v>
       </c>
       <c r="P5" t="s">
@@ -3075,42 +3370,42 @@
       <c r="T5" t="s">
         <v>349</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5">
         <v>2</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5">
         <v>473.36</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.043664713E7</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>10436647.130000001</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
@@ -3140,7 +3435,7 @@
       <c r="L6" t="s">
         <v>300</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>245.51</v>
       </c>
       <c r="P6" t="s">
@@ -3158,42 +3453,42 @@
       <c r="T6" t="s">
         <v>355</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
         <v>7441.2</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1168.62</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.04216345E7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="Y6">
+        <v>1168.6199999999999</v>
+      </c>
+      <c r="Z6">
+        <v>20421634.5</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
@@ -3223,7 +3518,7 @@
       <c r="L7" t="s">
         <v>300</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>27.28</v>
       </c>
       <c r="P7" t="s">
@@ -3241,42 +3536,42 @@
       <c r="T7" t="s">
         <v>360</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7">
         <v>1</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7">
         <v>1032.5</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y7">
         <v>279.62</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="Z7">
         <v>4886359.5</v>
       </c>
-      <c r="AA7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
@@ -3306,8 +3601,8 @@
       <c r="L8" t="s">
         <v>313</v>
       </c>
-      <c r="M8" t="n">
-        <v>11114.0</v>
+      <c r="M8">
+        <v>11114</v>
       </c>
       <c r="P8" t="s">
         <v>105</v>
@@ -3324,42 +3619,42 @@
       <c r="T8" t="s">
         <v>364</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U8">
         <v>4</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8">
         <v>46.14</v>
       </c>
-      <c r="Y8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
         <v>4043333.47</v>
       </c>
-      <c r="AC8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>120</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
@@ -3389,8 +3684,8 @@
       <c r="L9" t="s">
         <v>309</v>
       </c>
-      <c r="M9" t="n">
-        <v>4631.0</v>
+      <c r="M9">
+        <v>4631</v>
       </c>
       <c r="P9" t="s">
         <v>105</v>
@@ -3407,42 +3702,42 @@
       <c r="T9" t="s">
         <v>368</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U9">
         <v>2</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9">
         <v>13.85</v>
       </c>
-      <c r="Y9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
         <v>391062.01</v>
       </c>
-      <c r="AC9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>122</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
@@ -3472,8 +3767,8 @@
       <c r="L10" t="s">
         <v>313</v>
       </c>
-      <c r="M10" t="n">
-        <v>253.0</v>
+      <c r="M10">
+        <v>253</v>
       </c>
       <c r="P10" t="s">
         <v>105</v>
@@ -3490,42 +3785,42 @@
       <c r="T10" t="s">
         <v>373</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
         <v>2797.1</v>
       </c>
-      <c r="Y10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2888185.0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>2888185</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>122</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>4</v>
       </c>
       <c r="D11" t="s">
@@ -3555,8 +3850,8 @@
       <c r="L11" t="s">
         <v>313</v>
       </c>
-      <c r="M11" t="n">
-        <v>4200.0</v>
+      <c r="M11">
+        <v>4200</v>
       </c>
       <c r="P11" t="s">
         <v>105</v>
@@ -3573,42 +3868,42 @@
       <c r="T11" t="s">
         <v>349</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>154.55</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1713894.0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>154.55000000000001</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>1713894</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>122</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>4</v>
       </c>
       <c r="D12" t="s">
@@ -3638,7 +3933,7 @@
       <c r="L12" t="s">
         <v>377</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>105.84</v>
       </c>
       <c r="P12" t="s">
@@ -3656,42 +3951,42 @@
       <c r="T12" t="s">
         <v>379</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
         <v>167.61</v>
       </c>
-      <c r="Y12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>767340.0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>767340</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>122</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
@@ -3721,7 +4016,7 @@
       <c r="L13" t="s">
         <v>377</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>54.6</v>
       </c>
       <c r="P13" t="s">
@@ -3739,42 +4034,42 @@
       <c r="T13" t="s">
         <v>349</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
         <v>108.72</v>
       </c>
-      <c r="Y13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>778050.0</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>778050</v>
+      </c>
+      <c r="AC13">
         <v>199.63</v>
       </c>
-      <c r="AD13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>122</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
@@ -3804,8 +4099,8 @@
       <c r="L14" t="s">
         <v>300</v>
       </c>
-      <c r="M14" t="n">
-        <v>71.4</v>
+      <c r="M14">
+        <v>71.400000000000006</v>
       </c>
       <c r="P14" t="s">
         <v>105</v>
@@ -3822,42 +4117,42 @@
       <c r="T14" t="s">
         <v>349</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
         <v>473.36</v>
       </c>
-      <c r="Y14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8291716.98</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>8291716.9800000004</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>122</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
@@ -3887,8 +4182,8 @@
       <c r="L15" t="s">
         <v>238</v>
       </c>
-      <c r="M15" t="n">
-        <v>10.12</v>
+      <c r="M15">
+        <v>10.119999999999999</v>
       </c>
       <c r="P15" t="s">
         <v>105</v>
@@ -3905,42 +4200,42 @@
       <c r="T15" t="s">
         <v>373</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
         <v>67.75</v>
       </c>
-      <c r="Y15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>111320.0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>111320</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>122</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
@@ -3970,8 +4265,8 @@
       <c r="L16" t="s">
         <v>313</v>
       </c>
-      <c r="M16" t="n">
-        <v>4200.0</v>
+      <c r="M16">
+        <v>4200</v>
       </c>
       <c r="P16" t="s">
         <v>105</v>
@@ -3988,42 +4283,42 @@
       <c r="T16" t="s">
         <v>349</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>78.9</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1285410.0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>1285410</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>122</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="s">
@@ -4053,8 +4348,8 @@
       <c r="L17" t="s">
         <v>300</v>
       </c>
-      <c r="M17" t="n">
-        <v>1050.0</v>
+      <c r="M17">
+        <v>1050</v>
       </c>
       <c r="P17" t="s">
         <v>105</v>
@@ -4071,42 +4366,42 @@
       <c r="T17" t="s">
         <v>390</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
         <v>10532.71</v>
       </c>
-      <c r="Y17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.1920826391E8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>119208263.91</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>124</v>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="s">
@@ -4136,7 +4431,7 @@
       <c r="L18" t="s">
         <v>377</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>273.56</v>
       </c>
       <c r="P18" t="s">
@@ -4154,42 +4449,42 @@
       <c r="T18" t="s">
         <v>349</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
         <v>108.72</v>
       </c>
-      <c r="Y18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>3898230.0</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>3898230</v>
+      </c>
+      <c r="AC18">
         <v>199.63</v>
       </c>
-      <c r="AD18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>124</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
@@ -4219,7 +4514,7 @@
       <c r="L19" t="s">
         <v>300</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>357.73</v>
       </c>
       <c r="P19" t="s">
@@ -4237,42 +4532,42 @@
       <c r="T19" t="s">
         <v>349</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
         <v>473.36</v>
       </c>
-      <c r="Y19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>4.154336019E7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>41543360.189999998</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>124</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
@@ -4302,8 +4597,8 @@
       <c r="L20" t="s">
         <v>313</v>
       </c>
-      <c r="M20" t="n">
-        <v>21043.0</v>
+      <c r="M20">
+        <v>21043</v>
       </c>
       <c r="P20" t="s">
         <v>105</v>
@@ -4320,42 +4615,42 @@
       <c r="T20" t="s">
         <v>349</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>78.9</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>6440210.15</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>6440210.1500000004</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>124</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>4</v>
       </c>
       <c r="D21" t="s">
@@ -4385,8 +4680,8 @@
       <c r="L21" t="s">
         <v>313</v>
       </c>
-      <c r="M21" t="n">
-        <v>21043.0</v>
+      <c r="M21">
+        <v>21043</v>
       </c>
       <c r="P21" t="s">
         <v>105</v>
@@ -4403,42 +4698,42 @@
       <c r="T21" t="s">
         <v>349</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>154.55</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>8587017.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>154.55000000000001</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>8587017.0099999998</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>124</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
@@ -4468,7 +4763,7 @@
       <c r="L22" t="s">
         <v>238</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>58.92</v>
       </c>
       <c r="P22" t="s">
@@ -4486,42 +4781,42 @@
       <c r="T22" t="s">
         <v>373</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
         <v>67.75</v>
       </c>
-      <c r="Y22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
         <v>648124.4</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>124</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" t="s">
@@ -4551,7 +4846,7 @@
       <c r="L23" t="s">
         <v>300</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>5260.75</v>
       </c>
       <c r="P23" t="s">
@@ -4569,42 +4864,42 @@
       <c r="T23" t="s">
         <v>390</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
         <v>10532.71</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>5.9726178514E8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>597261785.13999999</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>124</v>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
         <v>4</v>
       </c>
       <c r="D24" t="s">
@@ -4634,7 +4929,7 @@
       <c r="L24" t="s">
         <v>377</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>530.28</v>
       </c>
       <c r="P24" t="s">
@@ -4652,42 +4947,42 @@
       <c r="T24" t="s">
         <v>379</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
         <v>167.61</v>
       </c>
-      <c r="Y24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3844530.0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>3844530</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>124</v>
       </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
@@ -4717,8 +5012,8 @@
       <c r="L25" t="s">
         <v>313</v>
       </c>
-      <c r="M25" t="n">
-        <v>1246.0</v>
+      <c r="M25">
+        <v>1246</v>
       </c>
       <c r="P25" t="s">
         <v>105</v>
@@ -4735,42 +5030,42 @@
       <c r="T25" t="s">
         <v>373</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
         <v>2797.1</v>
       </c>
-      <c r="Y25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.422402577E7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>14224025.77</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>126</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>2</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
@@ -4800,7 +5095,7 @@
       <c r="L26" t="s">
         <v>300</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>200.2</v>
       </c>
       <c r="P26" t="s">
@@ -4818,42 +5113,42 @@
       <c r="T26" t="s">
         <v>392</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U26">
         <v>1</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V26">
         <v>678.5</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Y26">
         <v>2032.03</v>
       </c>
-      <c r="Z26" t="n">
-        <v>3.550972425E7</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="Z26">
+        <v>35509724.25</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>126</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>2</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
@@ -4883,7 +5178,7 @@
       <c r="L27" t="s">
         <v>300</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27">
         <v>1907.15</v>
       </c>
       <c r="P27" t="s">
@@ -4901,42 +5196,42 @@
       <c r="T27" t="s">
         <v>398</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U27">
         <v>1</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V27">
         <v>7052.98</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Y27">
         <v>9306.89</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1.6263790275E8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.6263790275E8</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="Z27">
+        <v>162637902.75</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>162637902.75</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>126</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
@@ -4966,7 +5261,7 @@
       <c r="L28" t="s">
         <v>300</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28">
         <v>162.25</v>
       </c>
       <c r="P28" t="s">
@@ -4984,42 +5279,42 @@
       <c r="T28" t="s">
         <v>392</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U28">
         <v>1</v>
       </c>
-      <c r="V28" t="n">
+      <c r="V28">
         <v>678.5</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Y28">
         <v>1646.84</v>
       </c>
-      <c r="Z28" t="n">
-        <v>2.8778529E7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="Z28">
+        <v>28778529</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>126</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>1</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
@@ -5049,7 +5344,7 @@
       <c r="L29" t="s">
         <v>300</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29">
         <v>1545.65</v>
       </c>
       <c r="P29" t="s">
@@ -5067,79 +5362,75 @@
       <c r="T29" t="s">
         <v>398</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U29">
         <v>1</v>
       </c>
-      <c r="V29" t="n">
+      <c r="V29">
         <v>7052.98</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y29">
         <v>7542.77</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1.3180990575E8</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.3180990575E8</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="Z29">
+        <v>131809905.75</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>131809905.75</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:Y14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5216,14 +5507,14 @@
         <v>235</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
@@ -5235,39 +5526,39 @@
       <c r="F2" t="s">
         <v>108</v>
       </c>
-      <c r="G2" t="n">
-        <v>11.0</v>
+      <c r="G2">
+        <v>11</v>
       </c>
       <c r="H2" t="s">
         <v>134</v>
       </c>
-      <c r="I2" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2617404.03</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0</v>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>2617404.0299999998</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2" t="s">
         <v>300</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>245.51</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
@@ -5279,39 +5570,39 @@
       <c r="F3" t="s">
         <v>109</v>
       </c>
-      <c r="G3" t="n">
-        <v>7500.0</v>
+      <c r="G3">
+        <v>7500</v>
       </c>
       <c r="H3" t="s">
         <v>132</v>
       </c>
-      <c r="I3" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1841325.0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0</v>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1841325</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3" t="s">
         <v>300</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>245.51</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>116</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -5323,39 +5614,39 @@
       <c r="F4" t="s">
         <v>108</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>7.5</v>
       </c>
       <c r="H4" t="s">
         <v>132</v>
       </c>
-      <c r="I4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>1531622.59</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.0</v>
+      <c r="L4">
+        <v>0</v>
       </c>
       <c r="M4" t="s">
         <v>300</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>245.51</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
@@ -5367,39 +5658,39 @@
       <c r="F5" t="s">
         <v>108</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>2.5</v>
       </c>
       <c r="H5" t="s">
         <v>134</v>
       </c>
-      <c r="I5" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>594864.55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.0</v>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>594864.55000000005</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
       </c>
       <c r="M5" t="s">
         <v>300</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>245.51</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
@@ -5411,39 +5702,39 @@
       <c r="F6" t="s">
         <v>108</v>
       </c>
-      <c r="G6" t="n">
-        <v>5.0</v>
+      <c r="G6">
+        <v>5</v>
       </c>
       <c r="H6" t="s">
         <v>132</v>
       </c>
-      <c r="I6" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>244317.98</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.0</v>
+      <c r="L6">
+        <v>0</v>
       </c>
       <c r="M6" t="s">
         <v>300</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>27.28</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
@@ -5455,39 +5746,39 @@
       <c r="F7" t="s">
         <v>108</v>
       </c>
-      <c r="G7" t="n">
-        <v>11.0</v>
+      <c r="G7">
+        <v>11</v>
       </c>
       <c r="H7" t="s">
         <v>134</v>
       </c>
-      <c r="I7" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>564374.52</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.0</v>
+      <c r="L7">
+        <v>0</v>
       </c>
       <c r="M7" t="s">
         <v>300</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>27.28</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
@@ -5499,39 +5790,39 @@
       <c r="F8" t="s">
         <v>108</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>2.5</v>
       </c>
       <c r="H8" t="s">
         <v>134</v>
       </c>
-      <c r="I8" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>128266.94</v>
       </c>
-      <c r="L8" t="n">
-        <v>0.0</v>
+      <c r="L8">
+        <v>0</v>
       </c>
       <c r="M8" t="s">
         <v>300</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>27.28</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>126</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
@@ -5543,39 +5834,39 @@
       <c r="F9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" t="n">
-        <v>11.0</v>
+      <c r="G9">
+        <v>11</v>
       </c>
       <c r="H9" t="s">
         <v>134</v>
       </c>
-      <c r="I9" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>4101373.15</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.0</v>
+      <c r="L9">
+        <v>0</v>
       </c>
       <c r="M9" t="s">
         <v>300</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>200.2</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>126</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
@@ -5587,39 +5878,39 @@
       <c r="F10" t="s">
         <v>108</v>
       </c>
-      <c r="G10" t="n">
-        <v>5.0</v>
+      <c r="G10">
+        <v>5</v>
       </c>
       <c r="H10" t="s">
         <v>132</v>
       </c>
-      <c r="I10" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>1775486.21</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.0</v>
+      <c r="L10">
+        <v>0</v>
       </c>
       <c r="M10" t="s">
         <v>300</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>200.2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>126</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
@@ -5631,39 +5922,39 @@
       <c r="F11" t="s">
         <v>108</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>2.5</v>
       </c>
       <c r="H11" t="s">
         <v>134</v>
       </c>
-      <c r="I11" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>932130.26</v>
       </c>
-      <c r="L11" t="n">
-        <v>0.0</v>
+      <c r="L11">
+        <v>0</v>
       </c>
       <c r="M11" t="s">
         <v>300</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>200.2</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>126</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
@@ -5675,39 +5966,39 @@
       <c r="F12" t="s">
         <v>108</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>2.5</v>
       </c>
       <c r="H12" t="s">
         <v>134</v>
       </c>
-      <c r="I12" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>755436.39</v>
       </c>
-      <c r="L12" t="n">
-        <v>0.0</v>
+      <c r="L12">
+        <v>0</v>
       </c>
       <c r="M12" t="s">
         <v>300</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>162.25</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>126</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
@@ -5719,39 +6010,39 @@
       <c r="F13" t="s">
         <v>108</v>
       </c>
-      <c r="G13" t="n">
-        <v>11.0</v>
+      <c r="G13">
+        <v>11</v>
       </c>
       <c r="H13" t="s">
         <v>134</v>
       </c>
-      <c r="I13" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>3323920.1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0.0</v>
+      <c r="L13">
+        <v>0</v>
       </c>
       <c r="M13" t="s">
         <v>300</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13">
         <v>162.25</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>126</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
@@ -5763,58 +6054,54 @@
       <c r="F14" t="s">
         <v>108</v>
       </c>
-      <c r="G14" t="n">
-        <v>5.0</v>
+      <c r="G14">
+        <v>5</v>
       </c>
       <c r="H14" t="s">
         <v>132</v>
       </c>
-      <c r="I14" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>1438926.45</v>
       </c>
-      <c r="L14" t="n">
-        <v>0.0</v>
+      <c r="L14">
+        <v>0</v>
       </c>
       <c r="M14" t="s">
         <v>300</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14">
         <v>162.25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5835,31 +6122,27 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5876,7 +6159,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -5886,11 +6169,11 @@
       <c r="C2" t="s">
         <v>133</v>
       </c>
-      <c r="D2" t="n">
-        <v>1776000.0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="D2">
+        <v>1776000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -5900,11 +6183,11 @@
       <c r="C3" t="s">
         <v>135</v>
       </c>
-      <c r="D3" t="n">
-        <v>3182000.0</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="D3">
+        <v>3182000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>116</v>
       </c>
@@ -5914,11 +6197,11 @@
       <c r="C4" t="s">
         <v>136</v>
       </c>
-      <c r="D4" t="n">
-        <v>724000.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="D4">
+        <v>724000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -5928,11 +6211,11 @@
       <c r="C5" t="s">
         <v>137</v>
       </c>
-      <c r="D5" t="n">
-        <v>1842000.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="D5">
+        <v>1842000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>126</v>
       </c>
@@ -5942,11 +6225,11 @@
       <c r="C6" t="s">
         <v>135</v>
       </c>
-      <c r="D6" t="n">
-        <v>7426000.0</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="D6">
+        <v>7426000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>126</v>
       </c>
@@ -5956,11 +6239,11 @@
       <c r="C7" t="s">
         <v>136</v>
       </c>
-      <c r="D7" t="n">
-        <v>1688000.0</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="D7">
+        <v>1688000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>126</v>
       </c>
@@ -5970,41 +6253,37 @@
       <c r="C8" t="s">
         <v>133</v>
       </c>
-      <c r="D8" t="n">
-        <v>3215000.0</v>
+      <c r="D8">
+        <v>3215000</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6037,27 +6316,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6072,41 +6347,37 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:P19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="31.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="108.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="108.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6156,7 +6427,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -6191,7 +6462,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -6220,7 +6491,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -6258,7 +6529,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -6296,7 +6567,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
@@ -6325,7 +6596,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
@@ -6354,7 +6625,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -6389,7 +6660,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>120</v>
       </c>
@@ -6418,7 +6689,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>120</v>
       </c>
@@ -6456,7 +6727,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>122</v>
       </c>
@@ -6491,7 +6762,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>122</v>
       </c>
@@ -6529,7 +6800,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>122</v>
       </c>
@@ -6558,7 +6829,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>124</v>
       </c>
@@ -6593,7 +6864,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>124</v>
       </c>
@@ -6622,7 +6893,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -6660,7 +6931,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>126</v>
       </c>
@@ -6689,7 +6960,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>126</v>
       </c>
@@ -6724,7 +6995,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>126</v>
       </c>
@@ -6763,58 +7034,50 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>427</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6828,7 +7091,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -6842,7 +7105,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -6856,7 +7119,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>120</v>
       </c>
@@ -6870,7 +7133,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -6884,7 +7147,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -6898,7 +7161,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -6913,32 +7176,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6961,12 +7220,12 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
-        <v>1.0</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>182</v>
@@ -6978,12 +7237,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
-      <c r="B3" t="n">
-        <v>2.0</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>184</v>
@@ -6995,12 +7254,12 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="n">
-        <v>3.0</v>
+      <c r="B4">
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>105</v>
@@ -7012,12 +7271,12 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
-      <c r="B5" t="n">
-        <v>1.0</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>189</v>
@@ -7029,12 +7288,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
-      <c r="B6" t="n">
-        <v>2.0</v>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>191</v>
@@ -7046,12 +7305,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="n">
-        <v>3.0</v>
+      <c r="B7">
+        <v>3</v>
       </c>
       <c r="C7" t="s">
         <v>182</v>
@@ -7063,12 +7322,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
-      <c r="B8" t="n">
-        <v>4.0</v>
+      <c r="B8">
+        <v>4</v>
       </c>
       <c r="C8" t="s">
         <v>194</v>
@@ -7080,12 +7339,12 @@
         <v>196</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>116</v>
       </c>
-      <c r="B9" t="n">
-        <v>5.0</v>
+      <c r="B9">
+        <v>5</v>
       </c>
       <c r="C9" t="s">
         <v>194</v>
@@ -7097,12 +7356,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>120</v>
       </c>
-      <c r="B10" t="n">
-        <v>1.0</v>
+      <c r="B10">
+        <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>184</v>
@@ -7114,12 +7373,12 @@
         <v>186</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>120</v>
       </c>
-      <c r="B11" t="n">
-        <v>2.0</v>
+      <c r="B11">
+        <v>2</v>
       </c>
       <c r="C11" t="s">
         <v>182</v>
@@ -7131,12 +7390,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>120</v>
       </c>
-      <c r="B12" t="n">
-        <v>3.0</v>
+      <c r="B12">
+        <v>3</v>
       </c>
       <c r="C12" t="s">
         <v>182</v>
@@ -7148,12 +7407,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>120</v>
       </c>
-      <c r="B13" t="n">
-        <v>4.0</v>
+      <c r="B13">
+        <v>4</v>
       </c>
       <c r="C13" t="s">
         <v>105</v>
@@ -7165,12 +7424,12 @@
         <v>202</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>120</v>
       </c>
-      <c r="B14" t="n">
-        <v>5.0</v>
+      <c r="B14">
+        <v>5</v>
       </c>
       <c r="C14" t="s">
         <v>105</v>
@@ -7182,12 +7441,12 @@
         <v>204</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>122</v>
       </c>
-      <c r="B15" t="n">
-        <v>6.0</v>
+      <c r="B15">
+        <v>6</v>
       </c>
       <c r="C15" t="s">
         <v>105</v>
@@ -7199,12 +7458,12 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>122</v>
       </c>
-      <c r="B16" t="n">
-        <v>7.0</v>
+      <c r="B16">
+        <v>7</v>
       </c>
       <c r="C16" t="s">
         <v>105</v>
@@ -7216,12 +7475,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>122</v>
       </c>
-      <c r="B17" t="n">
-        <v>8.0</v>
+      <c r="B17">
+        <v>8</v>
       </c>
       <c r="C17" t="s">
         <v>182</v>
@@ -7233,12 +7492,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>122</v>
       </c>
-      <c r="B18" t="n">
-        <v>9.0</v>
+      <c r="B18">
+        <v>9</v>
       </c>
       <c r="C18" t="s">
         <v>182</v>
@@ -7250,12 +7509,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>122</v>
       </c>
-      <c r="B19" t="n">
-        <v>10.0</v>
+      <c r="B19">
+        <v>10</v>
       </c>
       <c r="C19" t="s">
         <v>182</v>
@@ -7267,12 +7526,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>122</v>
       </c>
-      <c r="B20" t="n">
-        <v>1.0</v>
+      <c r="B20">
+        <v>1</v>
       </c>
       <c r="C20" t="s">
         <v>189</v>
@@ -7284,12 +7543,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>122</v>
       </c>
-      <c r="B21" t="n">
-        <v>2.0</v>
+      <c r="B21">
+        <v>2</v>
       </c>
       <c r="C21" t="s">
         <v>184</v>
@@ -7301,12 +7560,12 @@
         <v>186</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>122</v>
       </c>
-      <c r="B22" t="n">
-        <v>3.0</v>
+      <c r="B22">
+        <v>3</v>
       </c>
       <c r="C22" t="s">
         <v>105</v>
@@ -7318,12 +7577,12 @@
         <v>188</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>122</v>
       </c>
-      <c r="B23" t="n">
-        <v>4.0</v>
+      <c r="B23">
+        <v>4</v>
       </c>
       <c r="C23" t="s">
         <v>105</v>
@@ -7335,12 +7594,12 @@
         <v>212</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>122</v>
       </c>
-      <c r="B24" t="n">
-        <v>5.0</v>
+      <c r="B24">
+        <v>5</v>
       </c>
       <c r="C24" t="s">
         <v>105</v>
@@ -7352,12 +7611,12 @@
         <v>214</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>124</v>
       </c>
-      <c r="B25" t="n">
-        <v>1.0</v>
+      <c r="B25">
+        <v>1</v>
       </c>
       <c r="C25" t="s">
         <v>189</v>
@@ -7369,12 +7628,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>124</v>
       </c>
-      <c r="B26" t="n">
-        <v>2.0</v>
+      <c r="B26">
+        <v>2</v>
       </c>
       <c r="C26" t="s">
         <v>184</v>
@@ -7386,12 +7645,12 @@
         <v>186</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>124</v>
       </c>
-      <c r="B27" t="n">
-        <v>3.0</v>
+      <c r="B27">
+        <v>3</v>
       </c>
       <c r="C27" t="s">
         <v>105</v>
@@ -7403,12 +7662,12 @@
         <v>188</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>124</v>
       </c>
-      <c r="B28" t="n">
-        <v>4.0</v>
+      <c r="B28">
+        <v>4</v>
       </c>
       <c r="C28" t="s">
         <v>105</v>
@@ -7420,12 +7679,12 @@
         <v>212</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>124</v>
       </c>
-      <c r="B29" t="n">
-        <v>5.0</v>
+      <c r="B29">
+        <v>5</v>
       </c>
       <c r="C29" t="s">
         <v>105</v>
@@ -7437,12 +7696,12 @@
         <v>214</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>124</v>
       </c>
-      <c r="B30" t="n">
-        <v>6.0</v>
+      <c r="B30">
+        <v>6</v>
       </c>
       <c r="C30" t="s">
         <v>105</v>
@@ -7454,12 +7713,12 @@
         <v>202</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>124</v>
       </c>
-      <c r="B31" t="n">
-        <v>7.0</v>
+      <c r="B31">
+        <v>7</v>
       </c>
       <c r="C31" t="s">
         <v>105</v>
@@ -7471,12 +7730,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>124</v>
       </c>
-      <c r="B32" t="n">
-        <v>8.0</v>
+      <c r="B32">
+        <v>8</v>
       </c>
       <c r="C32" t="s">
         <v>182</v>
@@ -7488,12 +7747,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>124</v>
       </c>
-      <c r="B33" t="n">
-        <v>9.0</v>
+      <c r="B33">
+        <v>9</v>
       </c>
       <c r="C33" t="s">
         <v>182</v>
@@ -7505,12 +7764,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>126</v>
       </c>
-      <c r="B34" t="n">
-        <v>1.0</v>
+      <c r="B34">
+        <v>1</v>
       </c>
       <c r="C34" t="s">
         <v>189</v>
@@ -7522,12 +7781,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>126</v>
       </c>
-      <c r="B35" t="n">
-        <v>2.0</v>
+      <c r="B35">
+        <v>2</v>
       </c>
       <c r="C35" t="s">
         <v>189</v>
@@ -7539,12 +7798,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>126</v>
       </c>
-      <c r="B36" t="n">
-        <v>3.0</v>
+      <c r="B36">
+        <v>3</v>
       </c>
       <c r="C36" t="s">
         <v>191</v>
@@ -7556,12 +7815,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>126</v>
       </c>
-      <c r="B37" t="n">
-        <v>4.0</v>
+      <c r="B37">
+        <v>4</v>
       </c>
       <c r="C37" t="s">
         <v>182</v>
@@ -7573,12 +7832,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>126</v>
       </c>
-      <c r="B38" t="n">
-        <v>5.0</v>
+      <c r="B38">
+        <v>5</v>
       </c>
       <c r="C38" t="s">
         <v>182</v>
@@ -7590,12 +7849,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>126</v>
       </c>
-      <c r="B39" t="n">
-        <v>6.0</v>
+      <c r="B39">
+        <v>6</v>
       </c>
       <c r="C39" t="s">
         <v>105</v>
@@ -7607,12 +7866,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>126</v>
       </c>
-      <c r="B40" t="n">
-        <v>7.0</v>
+      <c r="B40">
+        <v>7</v>
       </c>
       <c r="C40" t="s">
         <v>194</v>
@@ -7625,34 +7884,30 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7681,11 +7936,11 @@
         <v>232</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
@@ -7695,11 +7950,11 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
@@ -7709,11 +7964,11 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>120</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
@@ -7723,11 +7978,11 @@
         <v>192</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>122</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
@@ -7737,11 +7992,11 @@
         <v>192</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
@@ -7751,11 +8006,11 @@
         <v>192</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>126</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
@@ -7766,30 +8021,26 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7809,117 +8060,113 @@
         <v>237</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>238</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>122</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>238</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>12</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>120</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>239</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>122</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>239</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>253</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>239</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>1246</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>126</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>240</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>165</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7943,40 +8190,34 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8039,87 +8280,76 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:BR12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="126.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="59" max="59" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="68" max="68" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="69" max="69" width="30.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="126.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="47" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:70" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8331,11 +8561,11 @@
         <v>297</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
@@ -8362,60 +8592,60 @@
       <c r="J2" t="s">
         <v>300</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>114.05</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2">
         <v>114.05</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.324468238E7</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.0</v>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>13244682.380000001</v>
+      </c>
+      <c r="AA2">
+        <v>13244682.380000001</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>13244682.380000001</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
       </c>
       <c r="BR2" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -8442,60 +8672,60 @@
       <c r="J3" t="s">
         <v>300</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>1428.15</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3">
         <v>1428.15</v>
       </c>
-      <c r="V3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.24834768466E8</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.0</v>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>224834768.46599999</v>
+      </c>
+      <c r="AA3">
+        <v>224834768.46599999</v>
+      </c>
+      <c r="AB3">
+        <v>1</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>224834768.46599999</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
       </c>
       <c r="BR3" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
@@ -8522,60 +8752,60 @@
       <c r="J4" t="s">
         <v>300</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>1208.58</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4">
         <v>1208.58</v>
       </c>
-      <c r="V4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.902676921E8</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.0</v>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>190267692.09999999</v>
+      </c>
+      <c r="AA4">
+        <v>190267692.09999999</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>190267692.09999999</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
       </c>
       <c r="BR4" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>104</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
@@ -8602,60 +8832,60 @@
       <c r="J5" t="s">
         <v>300</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>89.87</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5">
         <v>89.87</v>
       </c>
-      <c r="V5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.043664713E7</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.0</v>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>10436647.130000001</v>
+      </c>
+      <c r="AA5">
+        <v>10436647.130000001</v>
+      </c>
+      <c r="AB5">
+        <v>1</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>10436647.130000001</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
       </c>
       <c r="BR5" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -8682,57 +8912,57 @@
       <c r="J6" t="s">
         <v>309</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>849.07</v>
       </c>
-      <c r="T6" t="n">
-        <v>272.79</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="T6">
+        <v>272.79000000000002</v>
+      </c>
+      <c r="Z6">
         <v>3260.43</v>
       </c>
-      <c r="AA6" t="n">
-        <v>5.697601425E7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>5.697601425E7</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.0</v>
+      <c r="AA6">
+        <v>56976014.25</v>
+      </c>
+      <c r="AB6">
+        <v>17475</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>56976014.25</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
       </c>
       <c r="BR6" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>120</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -8759,57 +8989,57 @@
       <c r="J7" t="s">
         <v>313</v>
       </c>
-      <c r="K7" t="n">
-        <v>11114.0</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="K7">
+        <v>11114</v>
+      </c>
+      <c r="T7">
         <v>14.9</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="Z7">
         <v>4043333.47</v>
       </c>
-      <c r="AI7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.0</v>
+      <c r="AA7">
+        <v>4043333.47</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>4043333.47</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
       </c>
       <c r="BR7" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
@@ -8836,57 +9066,57 @@
       <c r="J8" t="s">
         <v>309</v>
       </c>
-      <c r="K8" t="n">
-        <v>4631.0</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="K8">
+        <v>4631</v>
+      </c>
+      <c r="T8">
         <v>6.2</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="Z8">
         <v>391062.01</v>
       </c>
-      <c r="AI8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.0</v>
+      <c r="AA8">
+        <v>391062.01</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>391062.01</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
       </c>
       <c r="BR8" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>122</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
@@ -8913,63 +9143,63 @@
       <c r="J9" t="s">
         <v>313</v>
       </c>
-      <c r="K9" t="n">
-        <v>4200.0</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="K9">
+        <v>4200</v>
+      </c>
+      <c r="T9">
         <v>959.43</v>
       </c>
-      <c r="V9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2940.0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>5.13765E7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>5.13765E7</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.0</v>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>2940</v>
+      </c>
+      <c r="AA9">
+        <v>51376500</v>
+      </c>
+      <c r="AB9">
+        <v>17475</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>51376500</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
       </c>
       <c r="AW9" t="s">
         <v>108</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>0.0</v>
+      <c r="BJ9">
+        <v>0</v>
       </c>
       <c r="BR9" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>124</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
@@ -8996,63 +9226,63 @@
       <c r="J10" t="s">
         <v>313</v>
       </c>
-      <c r="K10" t="n">
-        <v>21043.0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4925.31</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="K10">
+        <v>21043</v>
+      </c>
+      <c r="T10">
+        <v>4925.3100000000004</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
         <v>14730.1</v>
       </c>
-      <c r="AA10" t="n">
-        <v>2.574084975E8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>2.574084975E8</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.0</v>
+      <c r="AA10">
+        <v>257408497.5</v>
+      </c>
+      <c r="AB10">
+        <v>17475</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>257408497.5</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
       </c>
       <c r="AW10" t="s">
         <v>108</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>0.0</v>
+      <c r="BJ10">
+        <v>0</v>
       </c>
       <c r="BR10" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>126</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
@@ -9079,57 +9309,57 @@
       <c r="J11" t="s">
         <v>309</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6122.74</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11">
         <v>1707.9</v>
       </c>
-      <c r="Z11" t="n">
-        <v>17572.26</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.070752435E8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3.070752435E8</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.0</v>
+      <c r="Z11">
+        <v>17572.259999999998</v>
+      </c>
+      <c r="AA11">
+        <v>307075243.5</v>
+      </c>
+      <c r="AB11">
+        <v>17475</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>307075243.5</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
       </c>
       <c r="BR11" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>126</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
@@ -9156,91 +9386,87 @@
       <c r="J12" t="s">
         <v>309</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>7263.47</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12">
         <v>2107.35</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z12">
         <v>20846.16</v>
       </c>
-      <c r="AA12" t="n">
-        <v>3.64286646E8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3.64286646E8</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.0</v>
+      <c r="AA12">
+        <v>364286646</v>
+      </c>
+      <c r="AB12">
+        <v>17475</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>364286646</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
       </c>
       <c r="BR12" t="s">
         <v>301</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9300,11 +9526,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>